--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AZ124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109585163</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109585269</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109585080</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109585063</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109582238</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767470</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111768781</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127597427</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132058290</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1781,6 +1831,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119571929</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119836238</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2038,6 +2098,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119836290</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2173,6 +2238,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119836308</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2280,6 +2350,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130974973</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2391,6 +2466,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883115</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2497,6 +2577,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883211</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2594,6 +2679,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133615777</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2700,6 +2790,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883203</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2806,6 +2901,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883228</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2912,6 +3012,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883233</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3014,6 +3119,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118761539</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3132,6 +3242,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/10749</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3242,6 +3357,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56200729</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3352,6 +3472,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56200727</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3449,6 +3574,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132075392</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3568,6 +3698,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775726</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3687,6 +3822,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775745</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3796,6 +3936,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106559324</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3897,6 +4042,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038203</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4008,6 +4158,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82209953</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4124,6 +4279,11 @@
       <c r="AY32" t="inlineStr">
         <is>
           <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109435564</t>
         </is>
       </c>
     </row>
@@ -4232,6 +4392,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82197781</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4343,6 +4508,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82201563</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4451,6 +4621,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111723460</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4558,6 +4733,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127425235</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4664,6 +4844,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127432966</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4779,6 +4964,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775792</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4898,6 +5088,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103869482</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5004,6 +5199,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038199</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5105,6 +5305,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128196759</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5206,6 +5411,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128196985</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5317,6 +5527,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82200093</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5423,6 +5638,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82206099</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5535,6 +5755,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421731</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5641,6 +5866,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127432891</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5742,6 +5972,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127432917</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5839,6 +6074,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75292121</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5958,6 +6198,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775337</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6064,6 +6309,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127432963</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6171,6 +6421,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82201838</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6278,6 +6533,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82202870</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6389,6 +6649,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86402248</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6500,6 +6765,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82200126</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6619,6 +6889,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775718</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6743,6 +7018,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103874694</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6849,6 +7129,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128196780</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6950,6 +7235,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128196830</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7056,6 +7346,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82201582</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7163,6 +7458,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118726511</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7274,6 +7574,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86402220</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7381,6 +7686,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118726412</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7492,6 +7802,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86402207</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7603,6 +7918,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86402264</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7710,6 +8030,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727827</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7817,6 +8142,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118726376</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7924,6 +8254,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118726761</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8039,6 +8374,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775423</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8154,6 +8494,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775741</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8255,6 +8600,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127432892</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8356,6 +8706,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128197028</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8462,6 +8817,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82197774</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8573,6 +8933,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775749</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8692,6 +9057,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103874685</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8801,6 +9171,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106561363</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8912,6 +9287,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82197735</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9018,6 +9398,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82197766</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9119,6 +9504,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128197031</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9225,6 +9615,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82201573</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9331,6 +9726,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82201498</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9432,6 +9832,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127432895</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9543,6 +9948,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82197723</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9662,6 +10072,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775339</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9771,6 +10186,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103869519</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9890,6 +10310,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775721</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10001,6 +10426,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120175371</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10112,6 +10542,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120175461</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10219,6 +10654,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127424941</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10325,6 +10765,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82210069</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10444,6 +10889,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775739</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10562,6 +11012,11 @@
           <t>Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122517840</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10681,6 +11136,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775421</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10797,6 +11257,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127425191</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10908,6 +11373,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82200101</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11017,6 +11487,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103869499</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11124,6 +11599,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120175726</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11231,6 +11711,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127424955</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11332,6 +11817,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128197034</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11441,6 +11931,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106561357</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11560,6 +12055,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775426</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11676,6 +12176,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421622</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11793,6 +12298,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118733229</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11913,6 +12423,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86403023</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12030,6 +12545,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118733231</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12153,6 +12673,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86402214</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12277,6 +12802,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103869419</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12379,6 +12909,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82210087</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12503,6 +13038,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86402245</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12615,6 +13155,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775793</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12726,6 +13271,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86402253</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12842,6 +13392,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103874700</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12940,6 +13495,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127432922</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13056,6 +13616,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103869454</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13167,6 +13732,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86402255</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13283,6 +13853,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103874704</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13399,6 +13974,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103874736</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13510,6 +14090,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86402258</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13627,6 +14212,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127423199</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13736,6 +14326,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106561408</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13855,6 +14450,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775356</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13956,6 +14556,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128196807</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14067,6 +14672,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82206136</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14178,6 +14788,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82206174</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14289,8 +14904,138 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82197748</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ123"/>
+  <dimension ref="A1:AZ124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14458,32 +14458,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>82206136</v>
+        <v>128196807</v>
       </c>
       <c r="B121" t="n">
-        <v>87297</v>
+        <v>91565</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003296</v>
+        <v>256756</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14492,17 +14492,17 @@
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>Pavolund, Vstm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>486836</v>
+        <v>486826</v>
       </c>
       <c r="R121" t="n">
-        <v>6585894</v>
+        <v>6585871</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14526,12 +14526,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14544,16 +14544,6 @@
       <c r="AG121" t="b">
         <v>0</v>
       </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>Lennart Söderberg</t>
-        </is>
-      </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
@@ -14562,19 +14552,19 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82206136</t>
+          <t>https://artportalen.se/Sighting/128196807</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>82206174</v>
+        <v>82206136</v>
       </c>
       <c r="B122" t="n">
         <v>87297</v>
@@ -14612,10 +14602,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>486847</v>
+        <v>486836</v>
       </c>
       <c r="R122" t="n">
-        <v>6585882</v>
+        <v>6585894</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14684,38 +14674,38 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82206174</t>
+          <t>https://artportalen.se/Sighting/82206136</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>82197748</v>
+        <v>82206174</v>
       </c>
       <c r="B123" t="n">
-        <v>91431</v>
+        <v>87297</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6039941</v>
+        <v>6003296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14728,10 +14718,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>486895</v>
+        <v>486847</v>
       </c>
       <c r="R123" t="n">
-        <v>6585559</v>
+        <v>6585882</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14758,12 +14748,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14794,11 +14784,127 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82206174</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>82197748</v>
+      </c>
+      <c r="B124" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Skathöjden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>486895</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6585559</v>
+      </c>
+      <c r="S124" t="n">
+        <v>25</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/82197748</t>
         </is>
@@ -14928,6 +15034,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -14461,7 +14461,7 @@
         <v>128196807</v>
       </c>
       <c r="B121" t="n">
-        <v>91565</v>
+        <v>91567</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ124"/>
+  <dimension ref="A1:AZ123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14458,32 +14458,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128196807</v>
+        <v>82206136</v>
       </c>
       <c r="B121" t="n">
-        <v>91567</v>
+        <v>87297</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>256756</v>
+        <v>6003296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14492,17 +14492,17 @@
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Pavolund, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>486826</v>
+        <v>486836</v>
       </c>
       <c r="R121" t="n">
-        <v>6585871</v>
+        <v>6585894</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14526,12 +14526,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14544,6 +14544,16 @@
       <c r="AG121" t="b">
         <v>0</v>
       </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>Lennart Söderberg</t>
+        </is>
+      </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
@@ -14552,19 +14562,19 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Toni Berglund, Anders Carlberg</t>
+          <t>Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128196807</t>
+          <t>https://artportalen.se/Sighting/82206136</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>82206136</v>
+        <v>82206174</v>
       </c>
       <c r="B122" t="n">
         <v>87297</v>
@@ -14602,10 +14612,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>486836</v>
+        <v>486847</v>
       </c>
       <c r="R122" t="n">
-        <v>6585894</v>
+        <v>6585882</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14674,38 +14684,38 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82206136</t>
+          <t>https://artportalen.se/Sighting/82206174</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>82206174</v>
+        <v>82197748</v>
       </c>
       <c r="B123" t="n">
-        <v>87297</v>
+        <v>91431</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6003296</v>
+        <v>6039941</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Gelatinfingersvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Ramaria primulina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14718,10 +14728,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>486847</v>
+        <v>486895</v>
       </c>
       <c r="R123" t="n">
-        <v>6585882</v>
+        <v>6585559</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14748,12 +14758,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14784,127 +14794,11 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/82206174</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>82197748</v>
-      </c>
-      <c r="B124" t="n">
-        <v>91431</v>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
-        <v>6039941</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Gelatinfingersvamp</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Ramaria primulina</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>Skathöjden, Vstm</t>
-        </is>
-      </c>
-      <c r="Q124" t="n">
-        <v>486895</v>
-      </c>
-      <c r="R124" t="n">
-        <v>6585559</v>
-      </c>
-      <c r="S124" t="n">
-        <v>25</v>
-      </c>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>Viker</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AD124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF124" t="inlineStr"/>
-      <c r="AG124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>Lennart Söderberg</t>
-        </is>
-      </c>
-      <c r="AT124" t="inlineStr"/>
-      <c r="AW124" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr"/>
-      <c r="AZ124" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/82197748</t>
         </is>
@@ -15034,7 +14928,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ123"/>
+  <dimension ref="A1:AZ124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14458,32 +14458,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>82206136</v>
+        <v>128196807</v>
       </c>
       <c r="B121" t="n">
-        <v>87297</v>
+        <v>91567</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003296</v>
+        <v>256756</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14492,17 +14492,17 @@
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>Pavolund, Vstm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>486836</v>
+        <v>486826</v>
       </c>
       <c r="R121" t="n">
-        <v>6585894</v>
+        <v>6585871</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14526,12 +14526,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14544,16 +14544,6 @@
       <c r="AG121" t="b">
         <v>0</v>
       </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>Lennart Söderberg</t>
-        </is>
-      </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
@@ -14562,19 +14552,19 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82206136</t>
+          <t>https://artportalen.se/Sighting/128196807</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>82206174</v>
+        <v>82206136</v>
       </c>
       <c r="B122" t="n">
         <v>87297</v>
@@ -14612,10 +14602,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>486847</v>
+        <v>486836</v>
       </c>
       <c r="R122" t="n">
-        <v>6585882</v>
+        <v>6585894</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14684,38 +14674,38 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82206174</t>
+          <t>https://artportalen.se/Sighting/82206136</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>82197748</v>
+        <v>82206174</v>
       </c>
       <c r="B123" t="n">
-        <v>91431</v>
+        <v>87297</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6039941</v>
+        <v>6003296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14728,10 +14718,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>486895</v>
+        <v>486847</v>
       </c>
       <c r="R123" t="n">
-        <v>6585559</v>
+        <v>6585882</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14758,12 +14748,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14794,11 +14784,127 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82206174</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>82197748</v>
+      </c>
+      <c r="B124" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Skathöjden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>486895</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6585559</v>
+      </c>
+      <c r="S124" t="n">
+        <v>25</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/82197748</t>
         </is>
@@ -14928,6 +15034,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ123"/>
+  <dimension ref="A1:AZ124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14458,32 +14458,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>82206136</v>
+        <v>128196807</v>
       </c>
       <c r="B121" t="n">
-        <v>87297</v>
+        <v>91569</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003296</v>
+        <v>256756</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14492,17 +14492,17 @@
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>Pavolund, Vstm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>486836</v>
+        <v>486826</v>
       </c>
       <c r="R121" t="n">
-        <v>6585894</v>
+        <v>6585871</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14526,12 +14526,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14544,16 +14544,6 @@
       <c r="AG121" t="b">
         <v>0</v>
       </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>Lennart Söderberg</t>
-        </is>
-      </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
@@ -14562,19 +14552,19 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82206136</t>
+          <t>https://artportalen.se/Sighting/128196807</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>82206174</v>
+        <v>82206136</v>
       </c>
       <c r="B122" t="n">
         <v>87297</v>
@@ -14612,10 +14602,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>486847</v>
+        <v>486836</v>
       </c>
       <c r="R122" t="n">
-        <v>6585882</v>
+        <v>6585894</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14684,38 +14674,38 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82206174</t>
+          <t>https://artportalen.se/Sighting/82206136</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>82197748</v>
+        <v>82206174</v>
       </c>
       <c r="B123" t="n">
-        <v>91431</v>
+        <v>87297</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6039941</v>
+        <v>6003296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14728,10 +14718,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>486895</v>
+        <v>486847</v>
       </c>
       <c r="R123" t="n">
-        <v>6585559</v>
+        <v>6585882</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14758,12 +14748,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14794,11 +14784,127 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82206174</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>82197748</v>
+      </c>
+      <c r="B124" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Skathöjden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>486895</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6585559</v>
+      </c>
+      <c r="S124" t="n">
+        <v>25</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/82197748</t>
         </is>
@@ -14928,6 +15034,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -14461,7 +14461,7 @@
         <v>128196807</v>
       </c>
       <c r="B121" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ124"/>
+  <dimension ref="A1:AZ123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14458,32 +14458,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128196807</v>
+        <v>82206136</v>
       </c>
       <c r="B121" t="n">
-        <v>91570</v>
+        <v>87297</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>256756</v>
+        <v>6003296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14492,17 +14492,17 @@
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Pavolund, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>486826</v>
+        <v>486836</v>
       </c>
       <c r="R121" t="n">
-        <v>6585871</v>
+        <v>6585894</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14526,12 +14526,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14544,6 +14544,16 @@
       <c r="AG121" t="b">
         <v>0</v>
       </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>Lennart Söderberg</t>
+        </is>
+      </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
@@ -14552,19 +14562,19 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Toni Berglund, Anders Carlberg</t>
+          <t>Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128196807</t>
+          <t>https://artportalen.se/Sighting/82206136</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>82206136</v>
+        <v>82206174</v>
       </c>
       <c r="B122" t="n">
         <v>87297</v>
@@ -14602,10 +14612,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>486836</v>
+        <v>486847</v>
       </c>
       <c r="R122" t="n">
-        <v>6585894</v>
+        <v>6585882</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14674,38 +14684,38 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82206136</t>
+          <t>https://artportalen.se/Sighting/82206174</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>82206174</v>
+        <v>82197748</v>
       </c>
       <c r="B123" t="n">
-        <v>87297</v>
+        <v>91431</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6003296</v>
+        <v>6039941</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Gelatinfingersvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Ramaria primulina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14718,10 +14728,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>486847</v>
+        <v>486895</v>
       </c>
       <c r="R123" t="n">
-        <v>6585882</v>
+        <v>6585559</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14748,12 +14758,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14784,127 +14794,11 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/82206174</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>82197748</v>
-      </c>
-      <c r="B124" t="n">
-        <v>91431</v>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
-        <v>6039941</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Gelatinfingersvamp</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Ramaria primulina</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>Skathöjden, Vstm</t>
-        </is>
-      </c>
-      <c r="Q124" t="n">
-        <v>486895</v>
-      </c>
-      <c r="R124" t="n">
-        <v>6585559</v>
-      </c>
-      <c r="S124" t="n">
-        <v>25</v>
-      </c>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>Viker</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AD124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF124" t="inlineStr"/>
-      <c r="AG124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>Lennart Söderberg</t>
-        </is>
-      </c>
-      <c r="AT124" t="inlineStr"/>
-      <c r="AW124" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr"/>
-      <c r="AZ124" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/82197748</t>
         </is>
@@ -15034,7 +14928,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ123"/>
+  <dimension ref="A1:AZ124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14458,32 +14458,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>82206136</v>
+        <v>128196807</v>
       </c>
       <c r="B121" t="n">
-        <v>87297</v>
+        <v>91571</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003296</v>
+        <v>256756</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14492,17 +14492,17 @@
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>Pavolund, Vstm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>486836</v>
+        <v>486826</v>
       </c>
       <c r="R121" t="n">
-        <v>6585894</v>
+        <v>6585871</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14526,12 +14526,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14544,16 +14544,6 @@
       <c r="AG121" t="b">
         <v>0</v>
       </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>Lennart Söderberg</t>
-        </is>
-      </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
@@ -14562,19 +14552,19 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82206136</t>
+          <t>https://artportalen.se/Sighting/128196807</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>82206174</v>
+        <v>82206136</v>
       </c>
       <c r="B122" t="n">
         <v>87297</v>
@@ -14612,10 +14602,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>486847</v>
+        <v>486836</v>
       </c>
       <c r="R122" t="n">
-        <v>6585882</v>
+        <v>6585894</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14684,38 +14674,38 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82206174</t>
+          <t>https://artportalen.se/Sighting/82206136</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>82197748</v>
+        <v>82206174</v>
       </c>
       <c r="B123" t="n">
-        <v>91431</v>
+        <v>87297</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6039941</v>
+        <v>6003296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14728,10 +14718,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>486895</v>
+        <v>486847</v>
       </c>
       <c r="R123" t="n">
-        <v>6585559</v>
+        <v>6585882</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14758,12 +14748,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14794,11 +14784,127 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82206174</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>82197748</v>
+      </c>
+      <c r="B124" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Skathöjden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>486895</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6585559</v>
+      </c>
+      <c r="S124" t="n">
+        <v>25</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/82197748</t>
         </is>
@@ -14928,6 +15034,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -14461,7 +14461,7 @@
         <v>128196807</v>
       </c>
       <c r="B121" t="n">
-        <v>91571</v>
+        <v>91572</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -14461,7 +14461,7 @@
         <v>128196807</v>
       </c>
       <c r="B121" t="n">
-        <v>91572</v>
+        <v>91578</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -14461,7 +14461,7 @@
         <v>128196807</v>
       </c>
       <c r="B121" t="n">
-        <v>91578</v>
+        <v>91579</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -14461,7 +14461,7 @@
         <v>128196807</v>
       </c>
       <c r="B121" t="n">
-        <v>91579</v>
+        <v>91585</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -14461,7 +14461,7 @@
         <v>128196807</v>
       </c>
       <c r="B121" t="n">
-        <v>91585</v>
+        <v>91592</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ124"/>
+  <dimension ref="A1:AZ128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6657,51 +6657,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>82200126</v>
+        <v>136443859</v>
       </c>
       <c r="B54" t="n">
-        <v>93234</v>
+        <v>96641</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1438</v>
+        <v>1078</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Slät taggsvamp</t>
+          <t>Rundfjädermossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon leucopus</t>
+          <t>Alleniella besseri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
+          <t>(Lobarz.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486849</v>
+        <v>486811</v>
       </c>
       <c r="R54" t="n">
-        <v>6585895</v>
+        <v>6585496</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6725,17 +6722,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>1 stort mycel, 15 fruktkroppar.</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6744,36 +6746,30 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82200126</t>
+          <t>https://artportalen.se/Sighting/136443859</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>95775718</v>
+        <v>82200126</v>
       </c>
       <c r="B55" t="n">
         <v>93234</v>
@@ -6801,16 +6797,8 @@
           <t>(Pers.) Maas Geest. &amp; Nannf.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -6819,10 +6807,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486846</v>
+        <v>486849</v>
       </c>
       <c r="R55" t="n">
-        <v>6585900</v>
+        <v>6585895</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6849,22 +6837,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2019-09-13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2019-09-13</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>1 stort mycel, 15 fruktkroppar.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6877,27 +6860,32 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95775718</t>
+          <t>https://artportalen.se/Sighting/82200126</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103874694</v>
+        <v>95775718</v>
       </c>
       <c r="B56" t="n">
         <v>93234</v>
@@ -6927,7 +6915,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6939,17 +6927,17 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ormtjärnen OSO om, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q56" t="n">
         <v>486846</v>
       </c>
       <c r="R56" t="n">
-        <v>6585889</v>
+        <v>6585900</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6973,17 +6961,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>återfynd</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6996,37 +6989,27 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Gräsgranskog</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund, Lennart Söderberg</t>
+          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103874694</t>
+          <t>https://artportalen.se/Sighting/95775718</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128196780</v>
+        <v>103874694</v>
       </c>
       <c r="B57" t="n">
         <v>93234</v>
@@ -7054,20 +7037,28 @@
           <t>(Pers.) Maas Geest. &amp; Nannf.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Pavolund, Vstm</t>
+          <t>Ormtjärnen OSO om, Vstm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486840</v>
+        <v>486846</v>
       </c>
       <c r="R57" t="n">
-        <v>6585890</v>
+        <v>6585889</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7094,17 +7085,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>3 nya fruktkroppar.</t>
+          <t>återfynd</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7117,52 +7108,62 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Gräsgranskog</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Toni Berglund, Anders Carlberg</t>
+          <t>Michael Andersson, Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128196780</t>
+          <t>https://artportalen.se/Sighting/103874694</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128196830</v>
+        <v>128196780</v>
       </c>
       <c r="B58" t="n">
-        <v>93231</v>
+        <v>93234</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1968</v>
+        <v>1438</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Slät taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Sarcodon leucopus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Pers.) Maas Geest. &amp; Nannf.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7175,10 +7176,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486853</v>
+        <v>486840</v>
       </c>
       <c r="R58" t="n">
-        <v>6585861</v>
+        <v>6585890</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7213,6 +7214,11 @@
           <t>2025-09-03</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>3 nya fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7237,54 +7243,51 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128196830</t>
+          <t>https://artportalen.se/Sighting/128196780</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>82201582</v>
+        <v>136445247</v>
       </c>
       <c r="B59" t="n">
-        <v>87322</v>
+        <v>93405</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1988</v>
+        <v>1440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>O Myggkärret, Vstm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486801</v>
+        <v>486875</v>
       </c>
       <c r="R59" t="n">
-        <v>6585457</v>
+        <v>6585498</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7311,12 +7314,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7325,77 +7338,74 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82201582</t>
+          <t>https://artportalen.se/Sighting/136445247</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118726511</v>
+        <v>128196830</v>
       </c>
       <c r="B60" t="n">
-        <v>97811</v>
+        <v>93231</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2604</v>
+        <v>1968</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>Pavolund, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486848</v>
+        <v>486853</v>
       </c>
       <c r="R60" t="n">
-        <v>6585869</v>
+        <v>6585861</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7419,22 +7429,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>16:16</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>16:16</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7443,61 +7443,61 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Toni Berglund, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118726511</t>
+          <t>https://artportalen.se/Sighting/128196830</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>86402220</v>
+        <v>82201582</v>
       </c>
       <c r="B61" t="n">
-        <v>97785</v>
+        <v>87322</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2606</v>
+        <v>1988</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7505,13 +7505,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486817</v>
+        <v>486801</v>
       </c>
       <c r="R61" t="n">
-        <v>6585851</v>
+        <v>6585457</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7535,22 +7535,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7559,33 +7549,39 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86402220</t>
+          <t>https://artportalen.se/Sighting/82201582</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118726412</v>
+        <v>118726511</v>
       </c>
       <c r="B62" t="n">
-        <v>97785</v>
+        <v>97811</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7593,21 +7589,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7688,16 +7684,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118726412</t>
+          <t>https://artportalen.se/Sighting/118726511</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>86402207</v>
+        <v>86402220</v>
       </c>
       <c r="B63" t="n">
-        <v>96437</v>
+        <v>97785</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7705,21 +7701,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7804,16 +7800,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86402207</t>
+          <t>https://artportalen.se/Sighting/86402220</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>86402264</v>
+        <v>118726412</v>
       </c>
       <c r="B64" t="n">
-        <v>96441</v>
+        <v>97785</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7821,41 +7817,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2668</v>
+        <v>2606</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486817</v>
+        <v>486848</v>
       </c>
       <c r="R64" t="n">
-        <v>6585851</v>
+        <v>6585869</v>
       </c>
       <c r="S64" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7879,22 +7871,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7920,16 +7912,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86402264</t>
+          <t>https://artportalen.se/Sighting/118726412</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118727827</v>
+        <v>136443734</v>
       </c>
       <c r="B65" t="n">
-        <v>96441</v>
+        <v>96644</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7937,21 +7929,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7961,13 +7953,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486836</v>
+        <v>486811</v>
       </c>
       <c r="R65" t="n">
-        <v>6585851</v>
+        <v>6585496</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7991,22 +7983,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8032,16 +8024,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118727827</t>
+          <t>https://artportalen.se/Sighting/136443734</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118726376</v>
+        <v>86402207</v>
       </c>
       <c r="B66" t="n">
-        <v>96186</v>
+        <v>96437</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8049,37 +8041,41 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2676</v>
+        <v>2667</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486848</v>
+        <v>486817</v>
       </c>
       <c r="R66" t="n">
-        <v>6585869</v>
+        <v>6585851</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8103,22 +8099,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8144,16 +8140,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118726376</t>
+          <t>https://artportalen.se/Sighting/86402207</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118726761</v>
+        <v>86402264</v>
       </c>
       <c r="B67" t="n">
-        <v>96186</v>
+        <v>96441</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8161,24 +8157,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2676</v>
+        <v>2668</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skathöjden, Vstm</t>
@@ -8215,22 +8215,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8256,16 +8256,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118726761</t>
+          <t>https://artportalen.se/Sighting/86402264</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>95775423</v>
+        <v>118727827</v>
       </c>
       <c r="B68" t="n">
-        <v>91680</v>
+        <v>96441</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8273,41 +8273,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3215</v>
+        <v>2668</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>O Myggkärret, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486875</v>
+        <v>486836</v>
       </c>
       <c r="R68" t="n">
-        <v>6585498</v>
+        <v>6585851</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8334,22 +8327,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8358,7 +8351,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8370,22 +8362,22 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg, Camilla Pettersson</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95775423</t>
+          <t>https://artportalen.se/Sighting/118727827</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>95775741</v>
+        <v>118726376</v>
       </c>
       <c r="B69" t="n">
-        <v>91680</v>
+        <v>96186</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8393,41 +8385,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3215</v>
+        <v>2676</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486833</v>
+        <v>486848</v>
       </c>
       <c r="R69" t="n">
-        <v>6585884</v>
+        <v>6585869</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8454,22 +8439,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8478,7 +8463,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8490,22 +8474,22 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95775741</t>
+          <t>https://artportalen.se/Sighting/118726376</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127432892</v>
+        <v>118726761</v>
       </c>
       <c r="B70" t="n">
-        <v>91680</v>
+        <v>96186</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8513,40 +8497,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3215</v>
+        <v>2676</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Pavolund, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486844</v>
+        <v>486817</v>
       </c>
       <c r="R70" t="n">
-        <v>6585882</v>
+        <v>6585851</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8570,12 +8551,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8584,31 +8575,30 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Toni Berglund, Anders Carlberg</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127432892</t>
+          <t>https://artportalen.se/Sighting/118726761</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128197028</v>
+        <v>95775423</v>
       </c>
       <c r="B71" t="n">
         <v>91680</v>
@@ -8637,22 +8627,26 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Pavolund, Vstm</t>
+          <t>O Myggkärret, Vstm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486853</v>
+        <v>486875</v>
       </c>
       <c r="R71" t="n">
-        <v>6585861</v>
+        <v>6585498</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8676,12 +8670,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8697,27 +8701,27 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Toni Berglund, Anders Carlberg</t>
+          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg, Camilla Pettersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128197028</t>
+          <t>https://artportalen.se/Sighting/95775423</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>82197774</v>
+        <v>95775741</v>
       </c>
       <c r="B72" t="n">
-        <v>87146</v>
+        <v>91680</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8725,25 +8729,29 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
@@ -8752,10 +8760,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>486903</v>
+        <v>486833</v>
       </c>
       <c r="R72" t="n">
-        <v>6585550</v>
+        <v>6585884</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8782,12 +8790,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8800,35 +8818,30 @@
       <c r="AG72" t="b">
         <v>0</v>
       </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
-      </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82197774</t>
+          <t>https://artportalen.se/Sighting/95775741</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>95775749</v>
+        <v>127432892</v>
       </c>
       <c r="B73" t="n">
-        <v>87146</v>
+        <v>91680</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8836,21 +8849,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8859,17 +8872,17 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>Pavolund, Vstm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486848</v>
+        <v>486844</v>
       </c>
       <c r="R73" t="n">
-        <v>6585869</v>
+        <v>6585882</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8893,22 +8906,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8924,27 +8927,27 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95775749</t>
+          <t>https://artportalen.se/Sighting/127432892</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>103874685</v>
+        <v>128197028</v>
       </c>
       <c r="B74" t="n">
-        <v>87146</v>
+        <v>91680</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8952,45 +8955,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ormtjärnen OSO om, Vstm</t>
+          <t>Pavolund, Vstm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486846</v>
+        <v>486853</v>
       </c>
       <c r="R74" t="n">
-        <v>6585889</v>
+        <v>6585861</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9017,12 +9012,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9035,37 +9030,27 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Gräsgranskog</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103874685</t>
+          <t>https://artportalen.se/Sighting/128197028</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>106561363</v>
+        <v>82197774</v>
       </c>
       <c r="B75" t="n">
         <v>87146</v>
@@ -9093,28 +9078,20 @@
           <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>SkathöjdenSV om Älvlången, Älvhyttan S om Venaån, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486829</v>
+        <v>486903</v>
       </c>
       <c r="R75" t="n">
-        <v>6585902</v>
+        <v>6585550</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9141,12 +9118,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9159,52 +9136,57 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lennart Söderberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lennart Söderberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106561363</t>
+          <t>https://artportalen.se/Sighting/82197774</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>82197735</v>
+        <v>95775749</v>
       </c>
       <c r="B76" t="n">
-        <v>93189</v>
+        <v>87146</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4361</v>
+        <v>3762</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9217,10 +9199,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486907</v>
+        <v>486848</v>
       </c>
       <c r="R76" t="n">
-        <v>6585579</v>
+        <v>6585869</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9247,17 +9229,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>6 kluster med fruktkroppar.</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9270,76 +9257,79 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
-      </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82197735</t>
+          <t>https://artportalen.se/Sighting/95775749</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>82197766</v>
+        <v>103874685</v>
       </c>
       <c r="B77" t="n">
-        <v>93189</v>
+        <v>87146</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4361</v>
+        <v>3762</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>Ormtjärnen OSO om, Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486895</v>
+        <v>486846</v>
       </c>
       <c r="R77" t="n">
-        <v>6585559</v>
+        <v>6585889</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9363,12 +9353,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9381,76 +9371,89 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Gräsgranskog</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82197766</t>
+          <t>https://artportalen.se/Sighting/103874685</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128197031</v>
+        <v>106561363</v>
       </c>
       <c r="B78" t="n">
-        <v>93189</v>
+        <v>87146</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4361</v>
+        <v>3762</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Pavolund, Vstm</t>
+          <t>SkathöjdenSV om Älvlången, Älvhyttan S om Venaån, Vstm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486853</v>
+        <v>486829</v>
       </c>
       <c r="R78" t="n">
-        <v>6585861</v>
+        <v>6585902</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9474,12 +9477,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9495,27 +9498,27 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Lennart Söderberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Toni Berglund, Anders Carlberg</t>
+          <t>Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128197031</t>
+          <t>https://artportalen.se/Sighting/106561363</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>82201573</v>
+        <v>82197735</v>
       </c>
       <c r="B79" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9523,21 +9526,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9550,10 +9553,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486797</v>
+        <v>486907</v>
       </c>
       <c r="R79" t="n">
-        <v>6585458</v>
+        <v>6585579</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9580,12 +9583,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>6 kluster med fruktkroppar.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9617,16 +9625,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82201573</t>
+          <t>https://artportalen.se/Sighting/82197735</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>82201498</v>
+        <v>82197766</v>
       </c>
       <c r="B80" t="n">
-        <v>93209</v>
+        <v>93189</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9634,21 +9642,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9661,10 +9669,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486846</v>
+        <v>486895</v>
       </c>
       <c r="R80" t="n">
-        <v>6585863</v>
+        <v>6585559</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9691,12 +9699,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9728,16 +9736,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82201498</t>
+          <t>https://artportalen.se/Sighting/82197766</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127432895</v>
+        <v>128197031</v>
       </c>
       <c r="B81" t="n">
-        <v>93209</v>
+        <v>93189</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9745,21 +9753,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9772,10 +9780,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486854</v>
+        <v>486853</v>
       </c>
       <c r="R81" t="n">
-        <v>6585862</v>
+        <v>6585861</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9802,12 +9810,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9834,16 +9842,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127432895</t>
+          <t>https://artportalen.se/Sighting/128197031</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>82197723</v>
+        <v>82201573</v>
       </c>
       <c r="B82" t="n">
-        <v>93215</v>
+        <v>93197</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9851,21 +9859,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9878,10 +9886,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486771</v>
+        <v>486797</v>
       </c>
       <c r="R82" t="n">
-        <v>6585673</v>
+        <v>6585458</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9908,17 +9916,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>1 mycel.</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9950,16 +9953,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82197723</t>
+          <t>https://artportalen.se/Sighting/82201573</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>95775339</v>
+        <v>136444091</v>
       </c>
       <c r="B83" t="n">
-        <v>93215</v>
+        <v>93386</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9967,48 +9970,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>O Myggkärret, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486897</v>
+        <v>486811</v>
       </c>
       <c r="R83" t="n">
-        <v>6585580</v>
+        <v>6585496</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10032,22 +10024,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10056,7 +10048,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10068,71 +10059,63 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg, Camilla Pettersson</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95775339</t>
+          <t>https://artportalen.se/Sighting/136444091</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>103869519</v>
+        <v>82201498</v>
       </c>
       <c r="B84" t="n">
-        <v>89143</v>
+        <v>93209</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4405</v>
+        <v>4366</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Ormtjärnen OSO om, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486831</v>
+        <v>486846</v>
       </c>
       <c r="R84" t="n">
-        <v>6585897</v>
+        <v>6585863</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10156,12 +10139,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10174,79 +10157,76 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103869519</t>
+          <t>https://artportalen.se/Sighting/82201498</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>95775721</v>
+        <v>127432895</v>
       </c>
       <c r="B85" t="n">
-        <v>88345</v>
+        <v>93209</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4566</v>
+        <v>4366</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dofttråding</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Inosperma bongardii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Weinm.) Matheny &amp; Estev-Rav.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>Pavolund, Vstm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486846</v>
+        <v>486854</v>
       </c>
       <c r="R85" t="n">
-        <v>6585900</v>
+        <v>6585862</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10270,22 +10250,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10301,49 +10271,49 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95775721</t>
+          <t>https://artportalen.se/Sighting/127432895</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120175371</v>
+        <v>82197723</v>
       </c>
       <c r="B86" t="n">
-        <v>88345</v>
+        <v>93215</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4566</v>
+        <v>4368</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dofttråding</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Inosperma bongardii</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Weinm.) Matheny &amp; Estev-Rav.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10356,10 +10326,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486848</v>
+        <v>486771</v>
       </c>
       <c r="R86" t="n">
-        <v>6585869</v>
+        <v>6585673</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10386,22 +10356,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>1 mycel.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10414,68 +10379,81 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Lennart Söderberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120175371</t>
+          <t>https://artportalen.se/Sighting/82197723</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120175461</v>
+        <v>95775339</v>
       </c>
       <c r="B87" t="n">
-        <v>92869</v>
+        <v>93215</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>O Myggkärret, Vstm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486848</v>
+        <v>486897</v>
       </c>
       <c r="R87" t="n">
-        <v>6585869</v>
+        <v>6585580</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10502,22 +10480,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10538,22 +10516,22 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Lennart Söderberg</t>
+          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg, Camilla Pettersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120175461</t>
+          <t>https://artportalen.se/Sighting/95775339</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127424941</v>
+        <v>103869519</v>
       </c>
       <c r="B88" t="n">
-        <v>92869</v>
+        <v>89143</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10561,37 +10539,48 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4769</v>
+        <v>4405</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>O Myggkärret, Vstm</t>
+          <t>Ormtjärnen OSO om, Vstm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486875</v>
+        <v>486831</v>
       </c>
       <c r="R88" t="n">
-        <v>6585498</v>
+        <v>6585897</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10615,22 +10604,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>17:25</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>17:25</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10639,59 +10618,68 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127424941</t>
+          <t>https://artportalen.se/Sighting/103869519</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>82210069</v>
+        <v>95775721</v>
       </c>
       <c r="B89" t="n">
-        <v>91424</v>
+        <v>88345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5733</v>
+        <v>4566</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Dofttråding</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Inosperma bongardii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+          <t>(Weinm.) Matheny &amp; Estev-Rav.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
@@ -10700,10 +10688,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486875</v>
+        <v>486846</v>
       </c>
       <c r="R89" t="n">
-        <v>6585533</v>
+        <v>6585900</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10730,12 +10718,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10748,69 +10746,56 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>marken, kalk, vid asp</t>
-        </is>
-      </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Toni Berglund, Lennart Söderberg</t>
+          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82210069</t>
+          <t>https://artportalen.se/Sighting/95775721</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>95775739</v>
+        <v>120175371</v>
       </c>
       <c r="B90" t="n">
-        <v>91409</v>
+        <v>88345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5741</v>
+        <v>4566</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Dofttråding</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Inosperma bongardii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Weinm.) Matheny &amp; Estev-Rav.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
@@ -10819,10 +10804,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486833</v>
+        <v>486848</v>
       </c>
       <c r="R90" t="n">
-        <v>6585884</v>
+        <v>6585869</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10849,22 +10834,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10885,68 +10870,60 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg</t>
+          <t>Anders Carlberg, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95775739</t>
+          <t>https://artportalen.se/Sighting/120175371</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122517840</v>
+        <v>120175461</v>
       </c>
       <c r="B91" t="n">
-        <v>91435</v>
+        <v>92869</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>SkathöjdenSV om Älvlången, Älvhyttan S om Venaån, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>486831</v>
+        <v>486848</v>
       </c>
       <c r="R91" t="n">
-        <v>6585897</v>
+        <v>6585869</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10973,24 +10950,29 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Högt upp på ett kalkblock. En miniatyr av arten.</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
@@ -10999,67 +10981,52 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lennart Söderberg</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lennart Söderberg</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
+          <t>Anders Carlberg, Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122517840</t>
+          <t>https://artportalen.se/Sighting/120175461</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>95775421</v>
+        <v>127424941</v>
       </c>
       <c r="B92" t="n">
-        <v>91443</v>
+        <v>92869</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5754</v>
+        <v>4769</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>O Myggkärret, Vstm</t>
@@ -11096,22 +11063,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11120,7 +11087,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11132,66 +11098,60 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg, Camilla Pettersson</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95775421</t>
+          <t>https://artportalen.se/Sighting/127424941</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127425191</v>
+        <v>82210069</v>
       </c>
       <c r="B93" t="n">
-        <v>92928</v>
+        <v>91424</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5836</v>
+        <v>5733</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Vent.) Schild</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>O Myggkärret, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>486897</v>
+        <v>486875</v>
       </c>
       <c r="R93" t="n">
-        <v>6585580</v>
+        <v>6585533</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11218,22 +11178,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>17:55</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>17:55</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11242,33 +11192,39 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>marken, kalk, vid asp</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127425191</t>
+          <t>https://artportalen.se/Sighting/82210069</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>82200101</v>
+        <v>95775739</v>
       </c>
       <c r="B94" t="n">
-        <v>93233</v>
+        <v>91409</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11276,25 +11232,33 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -11303,10 +11267,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>486841</v>
+        <v>486833</v>
       </c>
       <c r="R94" t="n">
-        <v>6585899</v>
+        <v>6585884</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11333,17 +11297,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar.</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11356,74 +11325,69 @@
       <c r="AG94" t="b">
         <v>0</v>
       </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
-      </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82200101</t>
+          <t>https://artportalen.se/Sighting/95775739</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>103869499</v>
+        <v>122517840</v>
       </c>
       <c r="B95" t="n">
-        <v>93233</v>
+        <v>91435</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ormtjärnen OSO om, Vstm</t>
+          <t>SkathöjdenSV om Älvlången, Älvhyttan S om Venaån, Vstm</t>
         </is>
       </c>
       <c r="Q95" t="n">
@@ -11433,7 +11397,7 @@
         <v>6585897</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11457,19 +11421,24 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Högt upp på ett kalkblock. En miniatyr av arten.</t>
         </is>
       </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
@@ -11478,27 +11447,31 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lennart Söderberg</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund, Lennart Söderberg</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103869499</t>
+          <t>https://artportalen.se/Sighting/122517840</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120175726</v>
+        <v>95775421</v>
       </c>
       <c r="B96" t="n">
-        <v>93233</v>
+        <v>91443</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11506,34 +11479,45 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>O Myggkärret, Vstm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>486846</v>
+        <v>486875</v>
       </c>
       <c r="R96" t="n">
-        <v>6585900</v>
+        <v>6585498</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11560,22 +11544,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11584,6 +11568,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11595,57 +11580,66 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Lennart Söderberg</t>
+          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg, Camilla Pettersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120175726</t>
+          <t>https://artportalen.se/Sighting/95775421</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127424955</v>
+        <v>127425191</v>
       </c>
       <c r="B97" t="n">
-        <v>93233</v>
+        <v>92928</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5964</v>
+        <v>5836</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>O Myggkärret, Vstm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>486875</v>
+        <v>486897</v>
       </c>
       <c r="R97" t="n">
-        <v>6585498</v>
+        <v>6585580</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11677,7 +11671,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11687,7 +11681,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11713,13 +11707,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127424955</t>
+          <t>https://artportalen.se/Sighting/127425191</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128197034</v>
+        <v>82200101</v>
       </c>
       <c r="B98" t="n">
         <v>93233</v>
@@ -11753,17 +11747,17 @@
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Pavolund, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>486853</v>
+        <v>486841</v>
       </c>
       <c r="R98" t="n">
-        <v>6585861</v>
+        <v>6585899</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11787,12 +11781,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2019-09-13</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2019-09-13</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11805,6 +11804,11 @@
       <c r="AG98" t="b">
         <v>0</v>
       </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
@@ -11813,71 +11817,71 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Toni Berglund, Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128197034</t>
+          <t>https://artportalen.se/Sighting/82200101</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>106561357</v>
+        <v>103869499</v>
       </c>
       <c r="B99" t="n">
-        <v>90721</v>
+        <v>93233</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6292</v>
+        <v>5964</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>SkathöjdenSV om Älvlången, Älvhyttan S om Venaån, Vstm</t>
+          <t>Ormtjärnen OSO om, Vstm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>486829</v>
+        <v>486831</v>
       </c>
       <c r="R99" t="n">
-        <v>6585902</v>
+        <v>6585897</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11901,12 +11905,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11922,27 +11926,27 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lennart Söderberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lennart Söderberg</t>
+          <t>Michael Andersson, Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106561357</t>
+          <t>https://artportalen.se/Sighting/103869499</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>95775426</v>
+        <v>120175726</v>
       </c>
       <c r="B100" t="n">
-        <v>58114</v>
+        <v>93233</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11950,46 +11954,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>O Myggkärret, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>486875</v>
+        <v>486846</v>
       </c>
       <c r="R100" t="n">
-        <v>6585498</v>
+        <v>6585900</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -12016,22 +12008,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12051,22 +12043,22 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg, Camilla Pettersson</t>
+          <t>Anders Carlberg, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95775426</t>
+          <t>https://artportalen.se/Sighting/120175726</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127421622</v>
+        <v>127424955</v>
       </c>
       <c r="B101" t="n">
-        <v>58114</v>
+        <v>93233</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12074,43 +12066,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>O Myggkärret, Vstm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>486848</v>
+        <v>486875</v>
       </c>
       <c r="R101" t="n">
-        <v>6585869</v>
+        <v>6585498</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -12142,7 +12125,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12152,7 +12135,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12172,69 +12155,63 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127421622</t>
+          <t>https://artportalen.se/Sighting/127424955</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118733229</v>
+        <v>128197034</v>
       </c>
       <c r="B102" t="n">
-        <v>58790</v>
+        <v>93233</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>208245</v>
+        <v>5964</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>Pavolund, Vstm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>486836</v>
+        <v>486853</v>
       </c>
       <c r="R102" t="n">
-        <v>6585851</v>
+        <v>6585861</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12258,22 +12235,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12289,27 +12256,27 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Toni Berglund, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118733229</t>
+          <t>https://artportalen.se/Sighting/128197034</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>86403023</v>
+        <v>106561357</v>
       </c>
       <c r="B103" t="n">
-        <v>58817</v>
+        <v>90721</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12317,21 +12284,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>208249</v>
+        <v>6292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12339,28 +12306,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>SkathöjdenSV om Älvlången, Älvhyttan S om Venaån, Vstm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>486817</v>
+        <v>486829</v>
       </c>
       <c r="R103" t="n">
-        <v>6585851</v>
+        <v>6585902</v>
       </c>
       <c r="S103" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12384,22 +12349,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12408,77 +12363,81 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Lennart Söderberg</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Toni Berglund, Anders Carlberg</t>
+          <t>Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86403023</t>
+          <t>https://artportalen.se/Sighting/106561357</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118733231</v>
+        <v>95775426</v>
       </c>
       <c r="B104" t="n">
-        <v>56884</v>
+        <v>58114</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>208255</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>O Myggkärret, Vstm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>486836</v>
+        <v>486875</v>
       </c>
       <c r="R104" t="n">
-        <v>6585851</v>
+        <v>6585498</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12505,22 +12464,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12529,7 +12488,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12541,76 +12499,69 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg, Camilla Pettersson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118733231</t>
+          <t>https://artportalen.se/Sighting/95775426</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>86402214</v>
+        <v>127421622</v>
       </c>
       <c r="B105" t="n">
-        <v>99093</v>
+        <v>58114</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219797</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>486817</v>
+        <v>486848</v>
       </c>
       <c r="R105" t="n">
-        <v>6585851</v>
+        <v>6585869</v>
       </c>
       <c r="S105" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12634,22 +12585,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12669,76 +12620,69 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86402214</t>
+          <t>https://artportalen.se/Sighting/127421622</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>103869419</v>
+        <v>118733229</v>
       </c>
       <c r="B106" t="n">
-        <v>110078</v>
+        <v>58790</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220299</v>
+        <v>208245</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Ormtjärnen OSO om, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>486837</v>
+        <v>486836</v>
       </c>
       <c r="R106" t="n">
-        <v>6585889</v>
+        <v>6585851</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12762,12 +12706,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12780,68 +12734,67 @@
       <c r="AG106" t="b">
         <v>0</v>
       </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Gräsgranskog</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>kalkgranskog med piprör dominerande i fältskiktet, med inslag av backskafting, gullris, stenbär, blåsippa, skogsvicker, smultron, gökärt, ärenpris, örnbräken, blodrot, harsyra, skogsviol, svinrot, blåbär, midsommarblomster och i det glesa buskskiktet rönn och olvon.</t>
-        </is>
-      </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103869419</t>
+          <t>https://artportalen.se/Sighting/118733229</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>82210087</v>
+        <v>86403023</v>
       </c>
       <c r="B107" t="n">
-        <v>102225</v>
+        <v>58817</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221223</v>
+        <v>208249</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -12849,13 +12802,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>486893</v>
+        <v>486817</v>
       </c>
       <c r="R107" t="n">
-        <v>6585594</v>
+        <v>6585851</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12879,12 +12832,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2020-06-21</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2020-06-21</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12893,70 +12856,66 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82210087</t>
+          <t>https://artportalen.se/Sighting/86403023</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>86402245</v>
+        <v>118733231</v>
       </c>
       <c r="B108" t="n">
-        <v>102225</v>
+        <v>56884</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221223</v>
+        <v>208255</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -12964,13 +12923,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>486817</v>
+        <v>486836</v>
       </c>
       <c r="R108" t="n">
         <v>6585851</v>
       </c>
       <c r="S108" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12994,27 +12953,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>minst</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13023,6 +12977,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13040,43 +12995,55 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86402245</t>
+          <t>https://artportalen.se/Sighting/118733231</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>95775793</v>
+        <v>86402214</v>
       </c>
       <c r="B109" t="n">
-        <v>102225</v>
+        <v>99093</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221223</v>
+        <v>219797</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
@@ -13085,13 +13052,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>486836</v>
+        <v>486817</v>
       </c>
       <c r="R109" t="n">
         <v>6585851</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13115,22 +13082,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13139,7 +13106,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -13151,22 +13117,22 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95775793</t>
+          <t>https://artportalen.se/Sighting/86402214</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>86402253</v>
+        <v>103869419</v>
       </c>
       <c r="B110" t="n">
-        <v>102241</v>
+        <v>110078</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13174,41 +13140,53 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221235</v>
+        <v>220299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>Ormtjärnen OSO om, Vstm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>486817</v>
+        <v>486837</v>
       </c>
       <c r="R110" t="n">
-        <v>6585851</v>
+        <v>6585889</v>
       </c>
       <c r="S110" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13232,22 +13210,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13256,33 +13224,44 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Gräsgranskog</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>kalkgranskog med piprör dominerande i fältskiktet, med inslag av backskafting, gullris, stenbär, blåsippa, skogsvicker, smultron, gökärt, ärenpris, örnbräken, blodrot, harsyra, skogsviol, svinrot, blåbär, midsommarblomster och i det glesa buskskiktet rönn och olvon.</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86402253</t>
+          <t>https://artportalen.se/Sighting/103869419</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>103874700</v>
+        <v>82210087</v>
       </c>
       <c r="B111" t="n">
-        <v>102241</v>
+        <v>102225</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13290,16 +13269,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221235</v>
+        <v>221223</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -13309,26 +13288,22 @@
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Ormtjärnen OSO om, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>486846</v>
+        <v>486893</v>
       </c>
       <c r="R111" t="n">
-        <v>6585889</v>
+        <v>6585594</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13352,12 +13327,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13370,78 +13345,80 @@
       <c r="AG111" t="b">
         <v>0</v>
       </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Gräsgranskog</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103874700</t>
+          <t>https://artportalen.se/Sighting/82210087</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127432922</v>
+        <v>86402245</v>
       </c>
       <c r="B112" t="n">
-        <v>97977</v>
+        <v>102225</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221944</v>
+        <v>221223</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Pavolund, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>486791</v>
+        <v>486817</v>
       </c>
       <c r="R112" t="n">
-        <v>6585837</v>
+        <v>6585851</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13465,12 +13442,27 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-06-21</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-06-21</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>minst</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13479,80 +13471,75 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Toni Berglund, Anders Carlberg</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127432922</t>
+          <t>https://artportalen.se/Sighting/86402245</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>103869454</v>
+        <v>95775793</v>
       </c>
       <c r="B113" t="n">
-        <v>103683</v>
+        <v>102225</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>222002</v>
+        <v>221223</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Ormtjärnen OSO om, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>486835</v>
+        <v>486836</v>
       </c>
       <c r="R113" t="n">
-        <v>6585898</v>
+        <v>6585851</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13576,12 +13563,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13594,62 +13591,52 @@
       <c r="AG113" t="b">
         <v>0</v>
       </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Gräsgranskog</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103869454</t>
+          <t>https://artportalen.se/Sighting/95775793</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>86402255</v>
+        <v>86402253</v>
       </c>
       <c r="B114" t="n">
-        <v>104628</v>
+        <v>102241</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13734,38 +13721,38 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86402255</t>
+          <t>https://artportalen.se/Sighting/86402253</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>103874704</v>
+        <v>103874700</v>
       </c>
       <c r="B115" t="n">
-        <v>101326</v>
+        <v>102241</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13855,16 +13842,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103874704</t>
+          <t>https://artportalen.se/Sighting/103874700</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>103874736</v>
+        <v>127432922</v>
       </c>
       <c r="B116" t="n">
-        <v>101326</v>
+        <v>97977</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13872,42 +13859,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Ormtjärnen OSO om, Vstm</t>
+          <t>Pavolund, Vstm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>486837</v>
+        <v>486791</v>
       </c>
       <c r="R116" t="n">
-        <v>6585889</v>
+        <v>6585837</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13934,12 +13913,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13952,40 +13931,30 @@
       <c r="AG116" t="b">
         <v>0</v>
       </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>Gräsgranskog</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund, Lennart Söderberg</t>
+          <t>Toni Berglund, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103874736</t>
+          <t>https://artportalen.se/Sighting/127432922</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>86402258</v>
+        <v>103869454</v>
       </c>
       <c r="B117" t="n">
-        <v>101228</v>
+        <v>103683</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13993,16 +13962,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>222771</v>
+        <v>222002</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -14012,22 +13981,26 @@
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>Ormtjärnen OSO om, Vstm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>486817</v>
+        <v>486835</v>
       </c>
       <c r="R117" t="n">
-        <v>6585851</v>
+        <v>6585898</v>
       </c>
       <c r="S117" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14051,22 +14024,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14075,33 +14038,44 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Gräsgranskog</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86402258</t>
+          <t>https://artportalen.se/Sighting/103869454</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127423199</v>
+        <v>86402255</v>
       </c>
       <c r="B118" t="n">
-        <v>97975</v>
+        <v>104628</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14109,21 +14083,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>224361</v>
+        <v>222412</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14133,17 +14107,17 @@
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Pavolund, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>486805</v>
+        <v>486817</v>
       </c>
       <c r="R118" t="n">
-        <v>6585845</v>
+        <v>6585851</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14167,27 +14141,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Rikliga bestånd på kalkblock. Få groddkorn men rikligt med sporangier.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14196,7 +14165,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -14214,65 +14182,62 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127423199</t>
+          <t>https://artportalen.se/Sighting/86402255</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>106561408</v>
+        <v>103874704</v>
       </c>
       <c r="B119" t="n">
-        <v>87099</v>
+        <v>101326</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>249278</v>
+        <v>222498</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>SkathöjdenSV om Älvlången, Älvhyttan S om Venaån, Vstm</t>
+          <t>Ormtjärnen OSO om, Vstm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>486829</v>
+        <v>486846</v>
       </c>
       <c r="R119" t="n">
-        <v>6585902</v>
+        <v>6585889</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14296,12 +14261,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14314,79 +14279,86 @@
       <c r="AG119" t="b">
         <v>0</v>
       </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Gräsgranskog</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Lennart Söderberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Lennart Söderberg</t>
+          <t>Michael Andersson, Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106561408</t>
+          <t>https://artportalen.se/Sighting/103874704</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>95775356</v>
+        <v>103874736</v>
       </c>
       <c r="B120" t="n">
-        <v>91420</v>
+        <v>101326</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>256335</v>
+        <v>222498</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>O Myggkärret, Vstm</t>
+          <t>Ormtjärnen OSO om, Vstm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>486900</v>
+        <v>486837</v>
       </c>
       <c r="R120" t="n">
-        <v>6585568</v>
+        <v>6585889</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14410,22 +14382,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14438,71 +14400,82 @@
       <c r="AG120" t="b">
         <v>0</v>
       </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Gräsgranskog</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg, Camilla Pettersson</t>
+          <t>Michael Andersson, Toni Berglund, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95775356</t>
+          <t>https://artportalen.se/Sighting/103874736</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128196807</v>
+        <v>86402258</v>
       </c>
       <c r="B121" t="n">
-        <v>91592</v>
+        <v>101228</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>256756</v>
+        <v>222771</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Pavolund, Vstm</t>
+          <t>Skathöjden, Vstm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>486826</v>
+        <v>486817</v>
       </c>
       <c r="R121" t="n">
-        <v>6585871</v>
+        <v>6585851</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14526,12 +14499,22 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2020-06-21</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2020-06-21</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14540,72 +14523,72 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Toni Berglund, Anders Carlberg</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128196807</t>
+          <t>https://artportalen.se/Sighting/86402258</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>82206136</v>
+        <v>127423199</v>
       </c>
       <c r="B122" t="n">
-        <v>87297</v>
+        <v>97975</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6003296</v>
+        <v>224361</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>Pavolund, Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>486836</v>
+        <v>486805</v>
       </c>
       <c r="R122" t="n">
-        <v>6585894</v>
+        <v>6585845</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14632,12 +14615,27 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Rikliga bestånd på kalkblock. Få groddkorn men rikligt med sporangier.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14650,78 +14648,76 @@
       <c r="AG122" t="b">
         <v>0</v>
       </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>Lennart Söderberg</t>
-        </is>
-      </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Toni Berglund, Lennart Söderberg</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82206136</t>
+          <t>https://artportalen.se/Sighting/127423199</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>82206174</v>
+        <v>106561408</v>
       </c>
       <c r="B123" t="n">
-        <v>87297</v>
+        <v>87099</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6003296</v>
+        <v>249278</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>SkathöjdenSV om Älvlången, Älvhyttan S om Venaån, Vstm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>486847</v>
+        <v>486829</v>
       </c>
       <c r="R123" t="n">
-        <v>6585882</v>
+        <v>6585902</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14748,12 +14744,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14766,78 +14762,76 @@
       <c r="AG123" t="b">
         <v>0</v>
       </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>Lennart Söderberg</t>
-        </is>
-      </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Lennart Söderberg</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Toni Berglund, Lennart Söderberg</t>
+          <t>Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82206174</t>
+          <t>https://artportalen.se/Sighting/106561408</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>82197748</v>
+        <v>95775356</v>
       </c>
       <c r="B124" t="n">
-        <v>91431</v>
+        <v>91420</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6039941</v>
+        <v>256335</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Skathöjden, Vstm</t>
+          <t>O Myggkärret, Vstm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>486895</v>
+        <v>486900</v>
       </c>
       <c r="R124" t="n">
-        <v>6585559</v>
+        <v>6585568</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14864,12 +14858,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14882,29 +14886,473 @@
       <c r="AG124" t="b">
         <v>0</v>
       </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>marken, kalk</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>Lennart Söderberg</t>
-        </is>
-      </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund, Lennart Söderberg, Camilla Pettersson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95775356</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128196807</v>
+      </c>
+      <c r="B125" t="n">
+        <v>91593</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Pavolund, Vstm</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>486826</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6585871</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Toni Berglund, Anders Carlberg</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128196807</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>82206136</v>
+      </c>
+      <c r="B126" t="n">
+        <v>87297</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6003296</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Stor odörspindling</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Cortinarius mussivus</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Skathöjden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>486836</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6585894</v>
+      </c>
+      <c r="S126" t="n">
+        <v>25</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2019-09-21</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2019-09-21</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Toni Berglund, Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82206136</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>82206174</v>
+      </c>
+      <c r="B127" t="n">
+        <v>87297</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6003296</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Stor odörspindling</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Cortinarius mussivus</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Skathöjden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>486847</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6585882</v>
+      </c>
+      <c r="S127" t="n">
+        <v>25</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2019-09-21</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2019-09-21</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Toni Berglund, Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82206174</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>82197748</v>
+      </c>
+      <c r="B128" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Skathöjden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>486895</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6585559</v>
+      </c>
+      <c r="S128" t="n">
+        <v>25</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>marken, kalk</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/82197748</t>
         </is>
@@ -15035,6 +15483,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -6660,7 +6660,7 @@
         <v>136443859</v>
       </c>
       <c r="B54" t="n">
-        <v>96641</v>
+        <v>96654</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136445247</v>
       </c>
       <c r="B59" t="n">
-        <v>93405</v>
+        <v>93418</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>136443734</v>
       </c>
       <c r="B65" t="n">
-        <v>96644</v>
+        <v>96657</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>136444091</v>
       </c>
       <c r="B83" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>128196807</v>
       </c>
       <c r="B125" t="n">
-        <v>91593</v>
+        <v>91606</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -6660,7 +6660,7 @@
         <v>136443859</v>
       </c>
       <c r="B54" t="n">
-        <v>96654</v>
+        <v>96655</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136445247</v>
       </c>
       <c r="B59" t="n">
-        <v>93418</v>
+        <v>93419</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>136443734</v>
       </c>
       <c r="B65" t="n">
-        <v>96657</v>
+        <v>96658</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>136444091</v>
       </c>
       <c r="B83" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>128196807</v>
       </c>
       <c r="B125" t="n">
-        <v>91606</v>
+        <v>91607</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Toni Berglund, Anders Carlberg</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
